--- a/results.xlsx
+++ b/results.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc2057430e44be2f/Documents/Year 4/Publishing/MATH3205_MPDPTW_Project-main/MATH3205_MPDPTW_Project-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="460" documentId="11_6131984955D9C33FDB66D9F0562E083178FA06C0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9B35A94-7AB0-4493-B19B-07DB20C3E408}"/>
+  <xr:revisionPtr revIDLastSave="758" documentId="11_6131984955D9C33FDB66D9F0562E083178FA06C0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6D28738-E02E-4299-8AEE-C63D19AA7268}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="205">
   <si>
     <t>Instance</t>
   </si>
@@ -626,6 +627,30 @@
   </si>
   <si>
     <t>Subset Size</t>
+  </si>
+  <si>
+    <t>Without</t>
+  </si>
+  <si>
+    <t>With</t>
+  </si>
+  <si>
+    <t>Routes Checked</t>
+  </si>
+  <si>
+    <t>Diff</t>
+  </si>
+  <si>
+    <t>Subproblem including Capacity Avg. Time (s)</t>
+  </si>
+  <si>
+    <t>Total avg. time with post capacity correction (s)</t>
+  </si>
+  <si>
+    <t>n_4_100</t>
+  </si>
+  <si>
+    <t>Avg Subproblems Ran</t>
   </si>
 </sst>
 </file>
@@ -841,6 +866,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1128,34 +1157,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X152"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Y152"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.73046875" customWidth="1"/>
+    <col min="3" max="3" width="23.86328125" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="36.5703125" customWidth="1"/>
-    <col min="6" max="6" width="26.85546875" customWidth="1"/>
-    <col min="7" max="7" width="26.5703125" customWidth="1"/>
-    <col min="8" max="8" width="32.7109375" customWidth="1"/>
-    <col min="9" max="10" width="36.5703125" customWidth="1"/>
-    <col min="11" max="11" width="25.140625" customWidth="1"/>
+    <col min="5" max="5" width="36.59765625" customWidth="1"/>
+    <col min="6" max="6" width="26.86328125" customWidth="1"/>
+    <col min="7" max="7" width="26.59765625" customWidth="1"/>
+    <col min="8" max="8" width="32.73046875" customWidth="1"/>
+    <col min="9" max="10" width="36.59765625" customWidth="1"/>
+    <col min="11" max="11" width="25.1328125" customWidth="1"/>
     <col min="12" max="12" width="27" customWidth="1"/>
-    <col min="13" max="13" width="18.85546875" customWidth="1"/>
-    <col min="14" max="14" width="26.140625" customWidth="1"/>
-    <col min="15" max="15" width="28.140625" customWidth="1"/>
+    <col min="13" max="13" width="18.86328125" customWidth="1"/>
+    <col min="14" max="14" width="26.1328125" customWidth="1"/>
+    <col min="15" max="15" width="28.1328125" customWidth="1"/>
     <col min="16" max="16" width="28" customWidth="1"/>
-    <col min="17" max="17" width="32.85546875" customWidth="1"/>
-    <col min="18" max="18" width="27.7109375" customWidth="1"/>
-    <col min="19" max="19" width="23.42578125" customWidth="1"/>
+    <col min="17" max="17" width="32.86328125" customWidth="1"/>
+    <col min="18" max="18" width="27.73046875" customWidth="1"/>
+    <col min="19" max="19" width="23.3984375" customWidth="1"/>
     <col min="20" max="20" width="31" customWidth="1"/>
-    <col min="21" max="21" width="28.5703125" customWidth="1"/>
-    <col min="23" max="23" width="23.42578125" customWidth="1"/>
-    <col min="24" max="24" width="25.42578125" customWidth="1"/>
+    <col min="21" max="21" width="28.59765625" customWidth="1"/>
+    <col min="23" max="23" width="23.3984375" customWidth="1"/>
+    <col min="24" max="24" width="25.3984375" customWidth="1"/>
     <col min="25" max="25" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1164,7 +1193,7 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
@@ -1215,7 +1244,7 @@
       </c>
       <c r="V2" s="9"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
@@ -1272,7 +1301,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
@@ -1329,7 +1358,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
@@ -1386,7 +1415,7 @@
         <v>305.5</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
@@ -1443,7 +1472,7 @@
         <v>3413.5</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
@@ -1493,7 +1522,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
@@ -1549,7 +1578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
@@ -1606,7 +1635,7 @@
         <v>378.5</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
@@ -1663,7 +1692,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
@@ -1713,7 +1742,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
@@ -1769,7 +1798,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
@@ -1826,7 +1855,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
@@ -1883,7 +1912,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
@@ -1940,7 +1969,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
@@ -1990,7 +2019,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
         <v>33</v>
       </c>
@@ -2040,7 +2069,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
         <v>34</v>
       </c>
@@ -2090,7 +2119,7 @@
         <v>203.8</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
         <v>35</v>
       </c>
@@ -2140,7 +2169,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
         <v>36</v>
       </c>
@@ -2190,7 +2219,7 @@
         <v>362.2</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
         <v>37</v>
       </c>
@@ -2240,7 +2269,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
         <v>38</v>
       </c>
@@ -2290,7 +2319,7 @@
         <v>318328.40000000002</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
         <v>39</v>
       </c>
@@ -2340,7 +2369,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
         <v>40</v>
       </c>
@@ -2390,7 +2419,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
         <v>41</v>
       </c>
@@ -2440,7 +2469,7 @@
         <v>107.6</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
         <v>42</v>
       </c>
@@ -2490,7 +2519,7 @@
         <v>2499.1999999999998</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B27" s="3" t="s">
         <v>43</v>
       </c>
@@ -2520,7 +2549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B28" s="3" t="s">
         <v>44</v>
       </c>
@@ -2550,7 +2579,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
         <v>45</v>
       </c>
@@ -2580,7 +2609,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
         <v>46</v>
       </c>
@@ -2610,7 +2639,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B31" s="3" t="s">
         <v>47</v>
       </c>
@@ -2652,7 +2681,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
@@ -2696,7 +2725,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B33" s="3" t="s">
         <v>52</v>
       </c>
@@ -2740,7 +2769,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B34" s="3" t="s">
         <v>54</v>
       </c>
@@ -2784,7 +2813,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B35" s="3" t="s">
         <v>56</v>
       </c>
@@ -2827,7 +2856,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
         <v>58</v>
       </c>
@@ -2869,7 +2898,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B37" s="3" t="s">
         <v>60</v>
       </c>
@@ -2911,7 +2940,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B38" s="3" t="s">
         <v>62</v>
       </c>
@@ -2953,7 +2982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B39" s="3" t="s">
         <v>64</v>
       </c>
@@ -2995,7 +3024,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B40" s="3" t="s">
         <v>66</v>
       </c>
@@ -3037,7 +3066,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B41" s="3" t="s">
         <v>67</v>
       </c>
@@ -3081,7 +3110,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B42" s="3" t="s">
         <v>69</v>
       </c>
@@ -3125,7 +3154,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B43" s="3" t="s">
         <v>71</v>
       </c>
@@ -3169,7 +3198,7 @@
         <v>90.8</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B44" s="3" t="s">
         <v>73</v>
       </c>
@@ -3208,7 +3237,7 @@
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B45" s="3" t="s">
         <v>75</v>
       </c>
@@ -3250,7 +3279,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B46" s="3" t="s">
         <v>77</v>
       </c>
@@ -3292,7 +3321,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B47" s="3" t="s">
         <v>79</v>
       </c>
@@ -3334,7 +3363,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B48" s="3" t="s">
         <v>81</v>
       </c>
@@ -3373,7 +3402,7 @@
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
     </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B49" s="3" t="s">
         <v>83</v>
       </c>
@@ -3403,7 +3432,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B50" s="3" t="s">
         <v>84</v>
       </c>
@@ -3433,7 +3462,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B51" s="3" t="s">
         <v>85</v>
       </c>
@@ -3463,7 +3492,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B52" s="3" t="s">
         <v>86</v>
       </c>
@@ -3493,7 +3522,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B53" s="3" t="s">
         <v>87</v>
       </c>
@@ -3523,7 +3552,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B54" s="3" t="s">
         <v>88</v>
       </c>
@@ -3553,7 +3582,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B55" s="3" t="s">
         <v>89</v>
       </c>
@@ -3598,7 +3627,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B56" s="3" t="s">
         <v>90</v>
       </c>
@@ -3633,7 +3662,7 @@
       </c>
       <c r="M56" s="15">
         <f>ROUND(D98,1)</f>
-        <v>19018.099999999999</v>
+        <v>18947.8</v>
       </c>
       <c r="N56" s="15">
         <f>E98</f>
@@ -3645,10 +3674,10 @@
       </c>
       <c r="P56">
         <f>(M56)/3600</f>
-        <v>5.2828055555555551</v>
-      </c>
-    </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
+        <v>5.2632777777777777</v>
+      </c>
+    </row>
+    <row r="57" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B57" s="3" t="s">
         <v>91</v>
       </c>
@@ -3683,7 +3712,7 @@
       </c>
       <c r="M57" s="15">
         <f>ROUND(D99,1)</f>
-        <v>44420.5</v>
+        <v>45051.199999999997</v>
       </c>
       <c r="N57" s="15">
         <f>E99</f>
@@ -3695,10 +3724,10 @@
       </c>
       <c r="P57">
         <f>(M57)/3600</f>
-        <v>12.339027777777778</v>
-      </c>
-    </row>
-    <row r="58" spans="2:21" x14ac:dyDescent="0.25">
+        <v>12.514222222222221</v>
+      </c>
+    </row>
+    <row r="58" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B58" s="3" t="s">
         <v>92</v>
       </c>
@@ -3733,7 +3762,7 @@
       </c>
       <c r="M58" s="15">
         <f>ROUND(D101,1)</f>
-        <v>63988.9</v>
+        <v>63257.3</v>
       </c>
       <c r="N58" s="15">
         <f>E101</f>
@@ -3745,10 +3774,10 @@
       </c>
       <c r="P58">
         <f>(M58)/3600</f>
-        <v>17.774694444444446</v>
-      </c>
-    </row>
-    <row r="59" spans="2:21" x14ac:dyDescent="0.25">
+        <v>17.571472222222223</v>
+      </c>
+    </row>
+    <row r="59" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B59" s="3" t="s">
         <v>93</v>
       </c>
@@ -3783,7 +3812,7 @@
       </c>
       <c r="M59" s="15">
         <f>ROUND(D102,1)</f>
-        <v>36173.300000000003</v>
+        <v>36312.400000000001</v>
       </c>
       <c r="N59" s="15">
         <f>E102</f>
@@ -3795,10 +3824,10 @@
       </c>
       <c r="P59">
         <f>(M59)/3600</f>
-        <v>10.048138888888889</v>
-      </c>
-    </row>
-    <row r="60" spans="2:21" x14ac:dyDescent="0.25">
+        <v>10.086777777777778</v>
+      </c>
+    </row>
+    <row r="60" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B60" s="3" t="s">
         <v>94</v>
       </c>
@@ -3828,7 +3857,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B61" s="3" t="s">
         <v>95</v>
       </c>
@@ -3861,7 +3890,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="62" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B62" s="3" t="s">
         <v>96</v>
       </c>
@@ -3921,7 +3950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B63" s="3" t="s">
         <v>97</v>
       </c>
@@ -3981,7 +4010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:21" x14ac:dyDescent="0.45">
       <c r="B64" s="3" t="s">
         <v>98</v>
       </c>
@@ -4041,7 +4070,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B65" s="3" t="s">
         <v>99</v>
       </c>
@@ -4109,8 +4138,9 @@
         <f>SUM($M$64:U64)</f>
         <v>18947.79</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="V65" s="18"/>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B66" s="3" t="s">
         <v>100</v>
       </c>
@@ -4140,7 +4170,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B67" s="3" t="s">
         <v>101</v>
       </c>
@@ -4173,7 +4203,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B68" s="3" t="s">
         <v>102</v>
       </c>
@@ -4239,7 +4269,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B69" s="3" t="s">
         <v>103</v>
       </c>
@@ -4305,7 +4335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B70" s="3" t="s">
         <v>104</v>
       </c>
@@ -4371,7 +4401,7 @@
         <v>16.29</v>
       </c>
     </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B71" s="3" t="s">
         <v>105</v>
       </c>
@@ -4447,8 +4477,9 @@
         <f>SUM($M70:W70)</f>
         <v>45051.189999999995</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="X71" s="18"/>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B72" s="3" t="s">
         <v>106</v>
       </c>
@@ -4478,7 +4509,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B73" s="3" t="s">
         <v>107</v>
       </c>
@@ -4508,7 +4539,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B74" s="3" t="s">
         <v>108</v>
       </c>
@@ -4541,7 +4572,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B75" s="3" t="s">
         <v>109</v>
       </c>
@@ -4610,7 +4641,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B76" s="3" t="s">
         <v>110</v>
       </c>
@@ -4679,7 +4710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B77" s="3" t="s">
         <v>111</v>
       </c>
@@ -4748,7 +4779,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B78" s="3" t="s">
         <v>112</v>
       </c>
@@ -4828,8 +4859,9 @@
         <f>SUM($M77:X77)</f>
         <v>63257.279999999999</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="Y78" s="18"/>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B79" s="3" t="s">
         <v>113</v>
       </c>
@@ -4859,7 +4891,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B80" s="3" t="s">
         <v>114</v>
       </c>
@@ -4892,7 +4924,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B81" s="3" t="s">
         <v>115</v>
       </c>
@@ -4958,7 +4990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B82" s="3" t="s">
         <v>116</v>
       </c>
@@ -5024,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B83" s="3" t="s">
         <v>117</v>
       </c>
@@ -5090,7 +5122,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B84" s="3" t="s">
         <v>118</v>
       </c>
@@ -5166,8 +5198,9 @@
         <f>SUM($M83:W83)</f>
         <v>36312.369999999995</v>
       </c>
-    </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X84" s="18"/>
+    </row>
+    <row r="85" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B85" s="3" t="s">
         <v>119</v>
       </c>
@@ -5197,7 +5230,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B86" s="3" t="s">
         <v>120</v>
       </c>
@@ -5227,7 +5260,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B87" s="3" t="s">
         <v>121</v>
       </c>
@@ -5257,7 +5290,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B88" s="3" t="s">
         <v>122</v>
       </c>
@@ -5287,7 +5320,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B89" s="3" t="s">
         <v>123</v>
       </c>
@@ -5317,7 +5350,7 @@
         <v>3256</v>
       </c>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B90" s="3" t="s">
         <v>124</v>
       </c>
@@ -5347,7 +5380,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B91" s="3" t="s">
         <v>125</v>
       </c>
@@ -5377,7 +5410,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B92" s="3" t="s">
         <v>126</v>
       </c>
@@ -5407,7 +5440,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B93" s="3" t="s">
         <v>127</v>
       </c>
@@ -5437,7 +5470,7 @@
         <v>7455</v>
       </c>
     </row>
-    <row r="94" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B94" s="3" t="s">
         <v>128</v>
       </c>
@@ -5467,7 +5500,7 @@
         <v>8250</v>
       </c>
     </row>
-    <row r="95" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B95" s="3" t="s">
         <v>129</v>
       </c>
@@ -5497,7 +5530,7 @@
         <v>5207</v>
       </c>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B96" s="3" t="s">
         <v>130</v>
       </c>
@@ -5527,7 +5560,7 @@
         <v>23814</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B97" s="3" t="s">
         <v>131</v>
       </c>
@@ -5557,7 +5590,7 @@
         <v>7020</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B98" s="3" t="s">
         <v>132</v>
       </c>
@@ -5565,7 +5598,8 @@
         <v>8084.85</v>
       </c>
       <c r="D98" s="2">
-        <v>19018.09</v>
+        <f>U65</f>
+        <v>18947.79</v>
       </c>
       <c r="E98" s="3">
         <v>13</v>
@@ -5587,7 +5621,7 @@
         <v>960258</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B99" s="3" t="s">
         <v>133</v>
       </c>
@@ -5595,7 +5629,8 @@
         <v>8938.98</v>
       </c>
       <c r="D99" s="2">
-        <v>44420.49</v>
+        <f>W71</f>
+        <v>45051.189999999995</v>
       </c>
       <c r="E99" s="3">
         <v>12</v>
@@ -5617,7 +5652,7 @@
         <v>1121784</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B100" s="3" t="s">
         <v>134</v>
       </c>
@@ -5647,7 +5682,7 @@
         <v>112776</v>
       </c>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B101" s="3" t="s">
         <v>135</v>
       </c>
@@ -5655,7 +5690,8 @@
         <v>7846.33</v>
       </c>
       <c r="D101" s="2">
-        <v>63988.94</v>
+        <f>X78</f>
+        <v>63257.279999999999</v>
       </c>
       <c r="E101" s="3">
         <v>4</v>
@@ -5677,7 +5713,7 @@
         <v>1899088</v>
       </c>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B102" s="3" t="s">
         <v>136</v>
       </c>
@@ -5685,7 +5721,8 @@
         <v>7793.58</v>
       </c>
       <c r="D102" s="2">
-        <v>36173.33</v>
+        <f>W84</f>
+        <v>36312.369999999995</v>
       </c>
       <c r="E102" s="3">
         <v>46</v>
@@ -5707,7 +5744,7 @@
         <v>1327688</v>
       </c>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B103" s="3" t="s">
         <v>138</v>
       </c>
@@ -5737,7 +5774,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B104" s="3" t="s">
         <v>139</v>
       </c>
@@ -5767,7 +5804,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B105" s="3" t="s">
         <v>140</v>
       </c>
@@ -5797,7 +5834,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B106" s="3" t="s">
         <v>141</v>
       </c>
@@ -5827,7 +5864,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B107" s="3" t="s">
         <v>142</v>
       </c>
@@ -5857,7 +5894,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B108" s="3" t="s">
         <v>143</v>
       </c>
@@ -5887,7 +5924,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B109" s="3" t="s">
         <v>144</v>
       </c>
@@ -5917,7 +5954,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B110" s="3" t="s">
         <v>145</v>
       </c>
@@ -5947,7 +5984,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B111" s="3" t="s">
         <v>146</v>
       </c>
@@ -5977,7 +6014,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B112" s="3" t="s">
         <v>147</v>
       </c>
@@ -6007,7 +6044,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B113" s="3" t="s">
         <v>148</v>
       </c>
@@ -6037,7 +6074,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B114" s="3" t="s">
         <v>149</v>
       </c>
@@ -6067,7 +6104,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B115" s="3" t="s">
         <v>150</v>
       </c>
@@ -6097,7 +6134,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B116" s="3" t="s">
         <v>151</v>
       </c>
@@ -6127,7 +6164,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B117" s="3" t="s">
         <v>152</v>
       </c>
@@ -6157,7 +6194,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B118" s="3" t="s">
         <v>153</v>
       </c>
@@ -6187,7 +6224,7 @@
         <v>8177</v>
       </c>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B119" s="3" t="s">
         <v>154</v>
       </c>
@@ -6217,7 +6254,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B120" s="3" t="s">
         <v>155</v>
       </c>
@@ -6247,7 +6284,7 @@
         <v>3275</v>
       </c>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B121" s="3" t="s">
         <v>156</v>
       </c>
@@ -6277,7 +6314,7 @@
         <v>10975</v>
       </c>
     </row>
-    <row r="122" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B122" s="6" t="s">
         <v>157</v>
       </c>
@@ -6307,7 +6344,7 @@
         <v>7674</v>
       </c>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B123" s="4" t="s">
         <v>158</v>
       </c>
@@ -6330,7 +6367,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B124" s="3" t="s">
         <v>159</v>
       </c>
@@ -6353,7 +6390,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B125" s="3" t="s">
         <v>160</v>
       </c>
@@ -6376,7 +6413,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B126" s="3" t="s">
         <v>161</v>
       </c>
@@ -6399,7 +6436,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B127" s="3" t="s">
         <v>162</v>
       </c>
@@ -6422,7 +6459,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B128" s="3" t="s">
         <v>163</v>
       </c>
@@ -6445,7 +6482,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B129" s="3" t="s">
         <v>164</v>
       </c>
@@ -6468,7 +6505,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B130" s="3" t="s">
         <v>165</v>
       </c>
@@ -6491,7 +6528,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B131" s="3" t="s">
         <v>166</v>
       </c>
@@ -6514,7 +6551,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B132" s="3" t="s">
         <v>167</v>
       </c>
@@ -6537,7 +6574,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B133" s="3" t="s">
         <v>168</v>
       </c>
@@ -6560,7 +6597,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B134" s="3" t="s">
         <v>169</v>
       </c>
@@ -6583,7 +6620,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B135" s="3" t="s">
         <v>170</v>
       </c>
@@ -6606,7 +6643,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B136" s="3" t="s">
         <v>171</v>
       </c>
@@ -6629,7 +6666,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B137" s="3" t="s">
         <v>172</v>
       </c>
@@ -6652,7 +6689,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B138" s="3" t="s">
         <v>173</v>
       </c>
@@ -6675,7 +6712,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B139" s="3" t="s">
         <v>174</v>
       </c>
@@ -6698,7 +6735,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B140" s="3" t="s">
         <v>175</v>
       </c>
@@ -6721,7 +6758,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B141" s="3" t="s">
         <v>176</v>
       </c>
@@ -6744,7 +6781,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B142" s="3" t="s">
         <v>177</v>
       </c>
@@ -6767,7 +6804,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B143" s="3" t="s">
         <v>178</v>
       </c>
@@ -6790,7 +6827,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B144" s="3" t="s">
         <v>179</v>
       </c>
@@ -6813,7 +6850,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B145" s="3" t="s">
         <v>180</v>
       </c>
@@ -6836,7 +6873,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B146" s="3" t="s">
         <v>181</v>
       </c>
@@ -6859,7 +6896,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B147" s="3" t="s">
         <v>182</v>
       </c>
@@ -6882,7 +6919,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B148" s="3" t="s">
         <v>183</v>
       </c>
@@ -6905,7 +6942,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B149" s="3" t="s">
         <v>184</v>
       </c>
@@ -6928,7 +6965,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B150" s="3" t="s">
         <v>185</v>
       </c>
@@ -6951,7 +6988,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B151" s="3" t="s">
         <v>186</v>
       </c>
@@ -6974,7 +7011,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B152" s="3" t="s">
         <v>187</v>
       </c>
@@ -7001,4 +7038,461 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4581EC4E-B8A4-47DA-9DBF-FD87C1F542B4}">
+  <dimension ref="B7:G33"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="22.1328125" customWidth="1"/>
+    <col min="3" max="3" width="54.1328125" customWidth="1"/>
+    <col min="4" max="4" width="28.86328125" customWidth="1"/>
+    <col min="5" max="5" width="32.265625" customWidth="1"/>
+    <col min="6" max="6" width="27.1328125" customWidth="1"/>
+    <col min="7" max="7" width="26.1328125" customWidth="1"/>
+    <col min="8" max="8" width="30.1328125" customWidth="1"/>
+    <col min="9" max="9" width="27.86328125" customWidth="1"/>
+    <col min="12" max="12" width="16.1328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="15">
+        <f>Sheet1!D18+Sheet1!G18</f>
+        <v>125.13</v>
+      </c>
+      <c r="D8" s="15">
+        <f>Sheet1!J18</f>
+        <v>13106</v>
+      </c>
+      <c r="E8" s="15">
+        <v>140.43</v>
+      </c>
+      <c r="F8" s="15">
+        <f>7329+5775</f>
+        <v>13104</v>
+      </c>
+      <c r="G8" s="15">
+        <f>D8-F8</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="15">
+        <f>Sheet1!D19+Sheet1!G19</f>
+        <v>521.37</v>
+      </c>
+      <c r="D9" s="15">
+        <f>Sheet1!J19</f>
+        <v>31696</v>
+      </c>
+      <c r="E9" s="15">
+        <v>723.32</v>
+      </c>
+      <c r="F9" s="15">
+        <f>21792+9899</f>
+        <v>31691</v>
+      </c>
+      <c r="G9" s="15">
+        <f>D9-F9</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="15">
+        <f>Sheet1!D20+Sheet1!G20</f>
+        <v>72.989999999999995</v>
+      </c>
+      <c r="D10" s="15">
+        <f>Sheet1!J20</f>
+        <v>5821</v>
+      </c>
+      <c r="E10" s="15">
+        <v>80.41</v>
+      </c>
+      <c r="F10" s="15">
+        <f>3033+2771</f>
+        <v>5804</v>
+      </c>
+      <c r="G10" s="15">
+        <f>D10-F10</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="15">
+        <f>Sheet1!D21+Sheet1!G21</f>
+        <v>371.95</v>
+      </c>
+      <c r="D11" s="15">
+        <f>Sheet1!J21</f>
+        <v>25727</v>
+      </c>
+      <c r="E11" s="15">
+        <v>453.75</v>
+      </c>
+      <c r="F11" s="15">
+        <f>18419+7284</f>
+        <v>25703</v>
+      </c>
+      <c r="G11" s="15">
+        <f>D11-F11</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="15">
+        <f>Sheet1!D22+Sheet1!G22</f>
+        <v>231.47</v>
+      </c>
+      <c r="D12" s="15">
+        <f>Sheet1!J22</f>
+        <v>15979</v>
+      </c>
+      <c r="E12" s="15">
+        <v>265.57</v>
+      </c>
+      <c r="F12" s="15">
+        <f>10014+5847</f>
+        <v>15861</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" ref="G12:G17" si="0">D12-F12</f>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B13" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="15">
+        <f>Sheet1!D118+Sheet1!G118</f>
+        <v>402.87</v>
+      </c>
+      <c r="D13" s="15">
+        <f>Sheet1!J118</f>
+        <v>8177</v>
+      </c>
+      <c r="E13" s="15">
+        <v>868.86</v>
+      </c>
+      <c r="F13" s="15">
+        <f>4211+2412</f>
+        <v>6623</v>
+      </c>
+      <c r="G13" s="15">
+        <f t="shared" si="0"/>
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B14" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="15">
+        <f>Sheet1!D119+Sheet1!G119</f>
+        <v>68.650000000000006</v>
+      </c>
+      <c r="D14" s="15">
+        <f>Sheet1!J119</f>
+        <v>2162</v>
+      </c>
+      <c r="E14" s="15">
+        <v>149.4</v>
+      </c>
+      <c r="F14" s="15">
+        <f>1104+767</f>
+        <v>1871</v>
+      </c>
+      <c r="G14" s="15">
+        <f t="shared" si="0"/>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B15" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="15">
+        <f>Sheet1!D120+Sheet1!G120</f>
+        <v>48.09</v>
+      </c>
+      <c r="D15" s="15">
+        <f>Sheet1!J120</f>
+        <v>3275</v>
+      </c>
+      <c r="E15" s="15">
+        <v>96.56</v>
+      </c>
+      <c r="F15" s="15">
+        <f>1713+1396</f>
+        <v>3109</v>
+      </c>
+      <c r="G15" s="15">
+        <f t="shared" si="0"/>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B16" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="15">
+        <f>Sheet1!D121+Sheet1!G121</f>
+        <v>262.7</v>
+      </c>
+      <c r="D16" s="15">
+        <f>Sheet1!J121</f>
+        <v>10975</v>
+      </c>
+      <c r="E16" s="15">
+        <v>419.96</v>
+      </c>
+      <c r="F16" s="15">
+        <f>5684+3162</f>
+        <v>8846</v>
+      </c>
+      <c r="G16" s="15">
+        <f t="shared" si="0"/>
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B17" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="15">
+        <f>Sheet1!D122+Sheet1!G122</f>
+        <v>98.48</v>
+      </c>
+      <c r="D17" s="15">
+        <f>Sheet1!J122</f>
+        <v>7674</v>
+      </c>
+      <c r="E17" s="15">
+        <v>218.73</v>
+      </c>
+      <c r="F17" s="15">
+        <f>4406+2734</f>
+        <v>7140</v>
+      </c>
+      <c r="G17" s="15">
+        <f t="shared" si="0"/>
+        <v>534</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="15">
+        <f>Sheet1!D58+Sheet1!G58</f>
+        <v>6.43</v>
+      </c>
+      <c r="D18" s="15">
+        <f>Sheet1!J58</f>
+        <v>2043</v>
+      </c>
+      <c r="E18" s="18">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="F18">
+        <f>1052+991</f>
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B19" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="15">
+        <f>Sheet1!D59+Sheet1!G59</f>
+        <v>40.26</v>
+      </c>
+      <c r="D19" s="15">
+        <f>Sheet1!J59</f>
+        <v>6273</v>
+      </c>
+      <c r="E19" s="18">
+        <v>46.09</v>
+      </c>
+      <c r="F19">
+        <f>4452+1821</f>
+        <v>6273</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="15">
+        <f>Sheet1!D60+Sheet1!G60</f>
+        <v>7.36</v>
+      </c>
+      <c r="D20" s="15">
+        <f>Sheet1!J60</f>
+        <v>1212</v>
+      </c>
+      <c r="E20" s="18">
+        <v>10.28</v>
+      </c>
+      <c r="F20">
+        <f>527+685</f>
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="15">
+        <f>Sheet1!D61+Sheet1!G61</f>
+        <v>16.48</v>
+      </c>
+      <c r="D21" s="15">
+        <f>Sheet1!J61</f>
+        <v>3508</v>
+      </c>
+      <c r="E21" s="18">
+        <v>19.79</v>
+      </c>
+      <c r="F21">
+        <f>2323+1185</f>
+        <v>3508</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B22" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="15">
+        <f>Sheet1!D62+Sheet1!G62</f>
+        <v>17.14</v>
+      </c>
+      <c r="D22" s="15">
+        <f>Sheet1!J62</f>
+        <v>3319</v>
+      </c>
+      <c r="E22" s="18">
+        <v>21.59</v>
+      </c>
+      <c r="F22">
+        <f>1959+1360</f>
+        <v>3319</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B30" s="15"/>
+      <c r="C30" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B31" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C31">
+        <f>AVERAGE(C18:C22)</f>
+        <v>17.533999999999999</v>
+      </c>
+      <c r="D31">
+        <f>ROUND(AVERAGE(D18:D22),1)</f>
+        <v>3271</v>
+      </c>
+      <c r="E31">
+        <f>AVERAGE(E18:E22)</f>
+        <v>21.26</v>
+      </c>
+      <c r="F31">
+        <f>ROUND(AVERAGE(F18:F22),1)</f>
+        <v>3271</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B32" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="15">
+        <f>ROUND(AVERAGE(C8:C12),2)</f>
+        <v>264.58</v>
+      </c>
+      <c r="D32" s="15">
+        <f>ROUND(AVERAGE(D8:D12),1)</f>
+        <v>18465.8</v>
+      </c>
+      <c r="E32" s="15">
+        <f>ROUND(AVERAGE(E8:E12),2)</f>
+        <v>332.7</v>
+      </c>
+      <c r="F32" s="15">
+        <f>ROUND(AVERAGE(F8:F12),1)</f>
+        <v>18432.599999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B33" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="15">
+        <f>ROUND(AVERAGE(C13:C17),1)</f>
+        <v>176.2</v>
+      </c>
+      <c r="D33" s="15">
+        <f>ROUND(AVERAGE(D13:D17),1)</f>
+        <v>6452.6</v>
+      </c>
+      <c r="E33" s="15">
+        <f>ROUND(AVERAGE(E13:E17),1)</f>
+        <v>350.7</v>
+      </c>
+      <c r="F33" s="15">
+        <f>ROUND(AVERAGE(F13:F17),1)</f>
+        <v>5517.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>